--- a/scripts/DoAn4_Bemori/AI/TestCase/TC/Excel/Sample_TestCase_NetaBooks.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/TC/Excel/Sample_TestCase_NetaBooks.xlsx
@@ -704,7 +704,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="75" customFormat="1" customHeight="1" s="14">
+    <row r="5" ht="90" customFormat="1" customHeight="1" s="14">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>TC_001</t>
@@ -712,12 +712,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công với thông tin hợp lệ</t>
+          <t>Kiểm tra đăng nhập thành công</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -726,7 +726,8 @@
 Step 2: Nhập email hợp lệ vào ô email
 Step 3: Nhập mật khẩu hợp lệ vào ô mật khẩu
 Step 4: Nhấn nút "Đăng nhập"
-Step 5: Kiểm tra rằng trang chủ NetaBooks được hiển thị thành công</t>
+Step 5: Kiểm tra chuyển hướng người dùng đến trang chủ NetaBooks
+Step 6: Kiểm tra trang chủ NetaBooks được hiển thị thành công</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -738,7 +739,7 @@
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -751,12 +752,12 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Đăng nhập khi không nhập email</t>
+          <t>Kiểm tra đăng nhập khi không nhập email</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -777,7 +778,7 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -790,12 +791,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Đăng nhập khi không nhập mật khẩu</t>
+          <t>Kiểm tra đăng nhập khi không nhập mật khẩu</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -816,7 +817,7 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -829,12 +830,12 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Đăng nhập với email sai định dạng</t>
+          <t>Kiểm tra đăng nhập khi email sai định dạng</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -855,7 +856,7 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="I8" s="11" t="n"/>
@@ -868,12 +869,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Đăng nhập với mật khẩu sai</t>
+          <t>Kiểm tra đăng nhập khi mật khẩu sai</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -894,7 +895,7 @@
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="I9" s="11" t="n"/>
